--- a/01_analyses_states/Andhra Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Andhra Pradesh/results/SoIB_summaries.xlsx
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -428,10 +428,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>80</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -444,10 +444,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="6">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C8">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Andhra Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Andhra Pradesh/results/SoIB_summaries.xlsx
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>18.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -428,10 +428,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>74.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -444,10 +444,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="6">
@@ -476,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C8">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Andhra Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Andhra Pradesh/results/SoIB_summaries.xlsx
@@ -396,10 +396,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3">
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="4">
@@ -428,10 +428,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>82.59999999999999</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="5">
@@ -444,10 +444,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>4.3</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="6">
@@ -476,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C8">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2">
-        <v>68</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>76.09999999999999</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="3">
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>29.1</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>23.9</v>
+        <v>22.3</v>
       </c>
     </row>
   </sheetData>
